--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/MONTANA_2020.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/MONTANA_2020.xlsx
@@ -690,7 +690,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C19">
